--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,105 +892,105 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
+        <v>100</v>
+      </c>
+      <c r="I15" s="14">
+        <v>3</v>
+      </c>
+      <c r="J15" s="14">
+        <v>2</v>
+      </c>
+      <c r="K15" s="15">
+        <v>50</v>
+      </c>
+      <c r="L15" s="15">
         <v>0</v>
       </c>
-      <c r="I15" s="14">
-        <v>1</v>
-      </c>
-      <c r="J15" s="14">
-        <v>1</v>
-      </c>
-      <c r="K15" s="15">
+      <c r="M15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="15">
         <v>0</v>
-      </c>
-      <c r="L15" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="15">
-        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-40</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J16" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.333333333333</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L16" s="15">
-        <v>-45.454545454545</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M16" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.304347826087</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>3</v>
-      </c>
-      <c r="D17" s="14">
-        <v>4</v>
-      </c>
-      <c r="E17" s="15">
+      <c r="C17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="14">
+        <v>6</v>
+      </c>
+      <c r="G17" s="14">
+        <v>8</v>
+      </c>
+      <c r="H17" s="15">
         <v>-25</v>
-      </c>
-      <c r="F17" s="14">
-        <v>7</v>
-      </c>
-      <c r="G17" s="14">
-        <v>13</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-46.153846153846</v>
       </c>
       <c r="I17" s="14">
         <v>11</v>
@@ -1002,13 +1002,13 @@
         <v>-35.294117647058</v>
       </c>
       <c r="L17" s="15">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="M17" s="15">
-        <v>-31.25</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="N17" s="15">
-        <v>-52.173913043478</v>
+        <v>-63.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,7 +1016,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1025,31 +1025,31 @@
         <v>21</v>
       </c>
       <c r="F18" s="14">
+        <v>5</v>
+      </c>
+      <c r="G18" s="14">
         <v>3</v>
       </c>
-      <c r="G18" s="14">
-        <v>4</v>
-      </c>
       <c r="H18" s="15">
-        <v>-25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J18" s="14">
         <v>7</v>
       </c>
       <c r="K18" s="15">
-        <v>-28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>-54.545454545454</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.285714285714</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.179487179487</v>
+        <v>-84.090909090909</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>44.444444444444</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H19" s="15">
-        <v>-2.5</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="I19" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J19" s="14">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.196721311475</v>
+        <v>-11.267605633802</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.196721311475</v>
+        <v>-16</v>
       </c>
       <c r="M19" s="15">
-        <v>-24.324324324324</v>
+        <v>-26.744186046511</v>
       </c>
       <c r="N19" s="15">
-        <v>-33.333333333333</v>
+        <v>-35.051546391752</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1109,11 +1109,11 @@
       <c r="F20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="14">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15">
-        <v>-100</v>
+      <c r="G20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I20" s="14">
         <v>1</v>
@@ -1125,13 +1125,13 @@
         <v>-50</v>
       </c>
       <c r="L20" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
       <c r="M20" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.113207547169</v>
+        <v>-98.461538461538</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>21.428571428571</v>
+        <v>-6.25</v>
       </c>
       <c r="F21" s="17">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G21" s="17">
         <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>-17.1875</v>
+        <v>-10.9375</v>
       </c>
       <c r="I21" s="17">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J21" s="17">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.525773195876</v>
+        <v>-16.814159292035</v>
       </c>
       <c r="L21" s="18">
-        <v>-20</v>
+        <v>-23.577235772357</v>
       </c>
       <c r="M21" s="18">
-        <v>-31.034482758620</v>
+        <v>-30.370370370370</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.479704797048</v>
+        <v>-70.063694267515</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="15">
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
+        <v>50</v>
+      </c>
+      <c r="I22" s="14">
+        <v>4</v>
+      </c>
+      <c r="J22" s="14">
+        <v>4</v>
+      </c>
+      <c r="K22" s="15">
         <v>0</v>
-      </c>
-      <c r="I22" s="14">
-        <v>2</v>
-      </c>
-      <c r="J22" s="14">
-        <v>3</v>
-      </c>
-      <c r="K22" s="15">
-        <v>-33.333333333333</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
-        <v>4</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-75</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-62.5</v>
+        <v>-40</v>
       </c>
       <c r="I23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="14">
         <v>9</v>
       </c>
       <c r="K23" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L23" s="15">
         <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>46.666666666666</v>
+        <v>25</v>
       </c>
       <c r="F24" s="14">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G24" s="14">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H24" s="15">
-        <v>12.121212121212</v>
+        <v>2.941176470588</v>
       </c>
       <c r="I24" s="14">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="J24" s="14">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="K24" s="15">
-        <v>9.090909090909</v>
+        <v>10</v>
       </c>
       <c r="L24" s="15">
-        <v>43.283582089552</v>
+        <v>32.530120481927</v>
       </c>
       <c r="M24" s="15">
-        <v>17.073170731707</v>
+        <v>15.789473684210</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G25" s="14">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H25" s="15">
-        <v>59.259259259259</v>
+        <v>25</v>
       </c>
       <c r="I25" s="14">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="J25" s="14">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="K25" s="15">
-        <v>64.864864864864</v>
+        <v>50</v>
       </c>
       <c r="L25" s="15">
-        <v>117.857142857143</v>
+        <v>89.473684210526</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>66.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F26" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H26" s="15">
-        <v>73.333333333333</v>
+        <v>27.777777777777</v>
       </c>
       <c r="I26" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J26" s="14">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K26" s="15">
-        <v>63.636363636363</v>
+        <v>44.827586206896</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.285714285714</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="M26" s="15">
-        <v>9.090909090909</v>
+        <v>13.513513513513</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>-66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,10 +1426,10 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
         <v>0</v>
@@ -1438,22 +1438,22 @@
         <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
+        <v>8</v>
+      </c>
+      <c r="J28" s="14">
         <v>6</v>
       </c>
-      <c r="J28" s="14">
-        <v>4</v>
-      </c>
       <c r="K28" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -893,122 +893,122 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>3</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="14">
         <v>5</v>
       </c>
-      <c r="E16" s="15">
-        <v>-40</v>
-      </c>
-      <c r="F16" s="14">
-        <v>6</v>
-      </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I16" s="14">
         <v>9</v>
       </c>
       <c r="J16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.714285714285</v>
+        <v>-40</v>
       </c>
       <c r="L16" s="15">
         <v>-30.769230769230</v>
       </c>
       <c r="M16" s="15">
-        <v>-25</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="N16" s="15">
-        <v>-88</v>
+        <v>-89.411764705882</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="C17" s="14">
+        <v>3</v>
+      </c>
+      <c r="D17" s="14">
+        <v>5</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-40</v>
       </c>
       <c r="F17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>-25</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J17" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K17" s="15">
-        <v>-35.294117647058</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L17" s="15">
-        <v>10</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>-42.105263157894</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N17" s="15">
-        <v>-63.333333333333</v>
+        <v>-56.25</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>4</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J18" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L18" s="15">
-        <v>-41.666666666666</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M18" s="15">
-        <v>-53.333333333333</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.090909090909</v>
+        <v>-85.964912280701</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.636363636363</v>
+        <v>-23.913043478260</v>
       </c>
       <c r="I19" s="14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J19" s="14">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.267605633802</v>
+        <v>-18.072289156626</v>
       </c>
       <c r="L19" s="15">
-        <v>-16</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M19" s="15">
-        <v>-26.744186046511</v>
+        <v>-25.274725274725</v>
       </c>
       <c r="N19" s="15">
-        <v>-35.051546391752</v>
+        <v>-40.350877192982</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1106,8 +1106,8 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>20</v>
+      <c r="F20" s="14">
+        <v>1</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1116,22 +1116,22 @@
         <v>21</v>
       </c>
       <c r="I20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="14">
         <v>2</v>
       </c>
       <c r="K20" s="15">
+        <v>0</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-80</v>
+      </c>
+      <c r="M20" s="15">
         <v>-50</v>
       </c>
-      <c r="L20" s="15">
-        <v>-90</v>
-      </c>
-      <c r="M20" s="15">
-        <v>-66.666666666666</v>
-      </c>
       <c r="N20" s="15">
-        <v>-98.461538461538</v>
+        <v>-97.402597402597</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-6.25</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
         <v>57</v>
       </c>
       <c r="G21" s="17">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.9375</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="J21" s="17">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.814159292035</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.577235772357</v>
+        <v>-24.460431654676</v>
       </c>
       <c r="M21" s="18">
-        <v>-30.370370370370</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.063694267515</v>
+        <v>-71.467391304347</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>100</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M22" s="15">
         <v>300</v>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J23" s="14">
         <v>9</v>
       </c>
       <c r="K23" s="15">
-        <v>-33.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
         <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G24" s="14">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H24" s="15">
-        <v>2.941176470588</v>
+        <v>17.1875</v>
       </c>
       <c r="I24" s="14">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="J24" s="14">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="K24" s="15">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="L24" s="15">
-        <v>32.530120481927</v>
+        <v>40</v>
       </c>
       <c r="M24" s="15">
-        <v>15.789473684210</v>
+        <v>14.545454545454</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G25" s="14">
         <v>36</v>
       </c>
       <c r="H25" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="J25" s="14">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="K25" s="15">
-        <v>50</v>
+        <v>37.931034482758</v>
       </c>
       <c r="L25" s="15">
-        <v>89.473684210526</v>
+        <v>90.476190476190</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>3</v>
+      </c>
+      <c r="D26" s="14">
         <v>6</v>
       </c>
-      <c r="D26" s="14">
-        <v>7</v>
-      </c>
       <c r="E26" s="15">
-        <v>-14.285714285714</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G26" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H26" s="15">
-        <v>27.777777777777</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J26" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K26" s="15">
-        <v>44.827586206896</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.545454545454</v>
+        <v>-15.094339622641</v>
       </c>
       <c r="M26" s="15">
-        <v>13.513513513513</v>
+        <v>4.651162790697</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
         <v>2</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,20 +1425,20 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
         <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-28.571428571428</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K16" s="15">
-        <v>-40</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.769230769230</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M16" s="15">
-        <v>-30.769230769230</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.411764705882</v>
+        <v>-89.130434782608</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-40</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>-41.666666666666</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I17" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J17" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K17" s="15">
-        <v>-36.363636363636</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L17" s="15">
-        <v>16.666666666666</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>-36.363636363636</v>
+        <v>-36</v>
       </c>
       <c r="N17" s="15">
-        <v>-56.25</v>
+        <v>-58.974358974359</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J18" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.272727272727</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L18" s="15">
-        <v>-38.461538461538</v>
+        <v>-37.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-52.941176470588</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.964912280701</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,45 +1060,45 @@
         <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-58.333333333333</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H19" s="15">
-        <v>-23.913043478260</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="I19" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J19" s="14">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.072289156626</v>
+        <v>-23.958333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.727272727272</v>
+        <v>-33.636363636363</v>
       </c>
       <c r="M19" s="15">
-        <v>-25.274725274725</v>
+        <v>-29.126213592233</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.350877192982</v>
+        <v>-45.112781954887</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1125,13 +1125,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="M20" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.402597402597</v>
+        <v>-97.701149425287</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>-76</v>
       </c>
       <c r="F21" s="17">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G21" s="17">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.833333333333</v>
+        <v>-33.766233766233</v>
       </c>
       <c r="I21" s="17">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="J21" s="17">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="K21" s="18">
-        <v>-22.222222222222</v>
+        <v>-28.125</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.460431654676</v>
+        <v>-33.139534883720</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.571428571428</v>
+        <v>-31.547619047619</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.467391304347</v>
+        <v>-72.941176470588</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,32 +1182,32 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="15">
         <v>300</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>2</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
         <v>8</v>
       </c>
       <c r="J23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="L23" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M23" s="15">
         <v>33.333333333333</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E24" s="15">
-        <v>33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="F24" s="14">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="G24" s="14">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="H24" s="15">
-        <v>17.1875</v>
+        <v>48.888888888888</v>
       </c>
       <c r="I24" s="14">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J24" s="14">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K24" s="15">
-        <v>12.5</v>
+        <v>17.796610169491</v>
       </c>
       <c r="L24" s="15">
-        <v>40</v>
+        <v>40.404040404040</v>
       </c>
       <c r="M24" s="15">
-        <v>14.545454545454</v>
+        <v>13.934426229508</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-20</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G25" s="14">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H25" s="15">
-        <v>33.333333333333</v>
+        <v>24.137931034482</v>
       </c>
       <c r="I25" s="14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J25" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K25" s="15">
-        <v>37.931034482758</v>
+        <v>39.344262295082</v>
       </c>
       <c r="L25" s="15">
-        <v>90.476190476190</v>
+        <v>88.888888888888</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>60</v>
       </c>
       <c r="F26" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G26" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>4.761904761904</v>
       </c>
       <c r="I26" s="14">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J26" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K26" s="15">
-        <v>28.571428571428</v>
+        <v>32.5</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.094339622641</v>
+        <v>-10.169491525423</v>
       </c>
       <c r="M26" s="15">
-        <v>4.651162790697</v>
+        <v>8.163265306122</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
         <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,23 +1557,23 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
         <v>33.333333333333</v>
@@ -926,130 +926,130 @@
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-100</v>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="14">
         <v>17</v>
       </c>
       <c r="K16" s="15">
-        <v>-41.176470588235</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.176470588235</v>
+        <v>-45</v>
       </c>
       <c r="M16" s="15">
-        <v>-23.076923076923</v>
+        <v>-31.25</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.130434782608</v>
+        <v>-90.350877192982</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>1</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H17" s="15">
-        <v>-38.461538461538</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I17" s="14">
         <v>16</v>
       </c>
       <c r="J17" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K17" s="15">
-        <v>-38.461538461538</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L17" s="15">
-        <v>6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>-36</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="N17" s="15">
-        <v>-58.974358974359</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.176470588235</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.5</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="M18" s="15">
-        <v>-54.545454545454</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.714285714285</v>
+        <v>-86.419753086419</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-61.538461538461</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G19" s="14">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H19" s="15">
-        <v>-31.818181818181</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I19" s="14">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="J19" s="14">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="K19" s="15">
-        <v>-23.958333333333</v>
+        <v>-25.663716814159</v>
       </c>
       <c r="L19" s="15">
-        <v>-33.636363636363</v>
+        <v>-28.813559322033</v>
       </c>
       <c r="M19" s="15">
-        <v>-29.126213592233</v>
+        <v>-30.578512396694</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.112781954887</v>
+        <v>-45.098039215686</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,7 +1107,7 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1116,22 +1116,22 @@
         <v>21</v>
       </c>
       <c r="I20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" s="14">
         <v>2</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L20" s="15">
-        <v>-81.818181818181</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="M20" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.701149425287</v>
+        <v>-96.907216494845</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-76</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="F21" s="17">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G21" s="17">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H21" s="18">
-        <v>-33.766233766233</v>
+        <v>-43.529411764705</v>
       </c>
       <c r="I21" s="17">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="J21" s="17">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="K21" s="18">
-        <v>-28.125</v>
+        <v>-29.120879120879</v>
       </c>
       <c r="L21" s="18">
-        <v>-33.139534883720</v>
+        <v>-31.016042780748</v>
       </c>
       <c r="M21" s="18">
-        <v>-31.547619047619</v>
+        <v>-34.183673469387</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.941176470588</v>
+        <v>-74.148296593186</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
@@ -1207,10 +1207,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M22" s="15">
-        <v>300</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,28 +1230,28 @@
         <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-20</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
         <v>8</v>
       </c>
       <c r="J23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K23" s="15">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L23" s="15">
+        <v>0</v>
+      </c>
+      <c r="M23" s="15">
         <v>14.285714285714</v>
-      </c>
-      <c r="M23" s="15">
-        <v>33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>150</v>
+        <v>12.5</v>
       </c>
       <c r="F24" s="14">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G24" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H24" s="15">
-        <v>48.888888888888</v>
+        <v>39.130434782608</v>
       </c>
       <c r="I24" s="14">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="J24" s="14">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="K24" s="15">
-        <v>17.796610169491</v>
+        <v>16.417910447761</v>
       </c>
       <c r="L24" s="15">
-        <v>40.404040404040</v>
+        <v>45.794392523364</v>
       </c>
       <c r="M24" s="15">
-        <v>13.934426229508</v>
+        <v>14.705882352941</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F25" s="14">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G25" s="14">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H25" s="15">
-        <v>24.137931034482</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="I25" s="14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J25" s="14">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="K25" s="15">
-        <v>39.344262295082</v>
+        <v>21.621621621621</v>
       </c>
       <c r="L25" s="15">
-        <v>88.888888888888</v>
+        <v>83.673469387755</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>60</v>
+        <v>266.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G26" s="14">
         <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>4.761904761904</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="J26" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K26" s="15">
-        <v>32.5</v>
+        <v>48.837209302325</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.169491525423</v>
+        <v>-1.538461538461</v>
       </c>
       <c r="M26" s="15">
-        <v>8.163265306122</v>
+        <v>16.363636363636</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
         <v>-20</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
@@ -1444,16 +1444,16 @@
         <v>-25</v>
       </c>
       <c r="I28" s="14">
+        <v>9</v>
+      </c>
+      <c r="J28" s="14">
         <v>8</v>
       </c>
-      <c r="J28" s="14">
-        <v>7</v>
-      </c>
       <c r="K28" s="15">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>0</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
@@ -920,7 +920,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -936,79 +936,79 @@
       <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="14">
+        <v>4</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-75</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.294117647058</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L16" s="15">
-        <v>-45</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M16" s="15">
-        <v>-31.25</v>
+        <v>-25</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.350877192982</v>
+        <v>-90.551181102362</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="14">
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G17" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>-54.545454545454</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J17" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K17" s="15">
-        <v>-42.857142857142</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="L17" s="15">
         <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>-40.740740740740</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="N17" s="15">
-        <v>-66.666666666666</v>
+        <v>-63.461538461538</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F18" s="14">
+        <v>5</v>
+      </c>
+      <c r="G18" s="14">
+        <v>15</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I18" s="14">
+        <v>13</v>
+      </c>
+      <c r="J18" s="14">
+        <v>22</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-40.909090909090</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-35</v>
+      </c>
+      <c r="M18" s="15">
         <v>-50</v>
       </c>
-      <c r="F18" s="14">
-        <v>6</v>
-      </c>
-      <c r="G18" s="14">
-        <v>12</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-50</v>
-      </c>
-      <c r="I18" s="14">
-        <v>11</v>
-      </c>
-      <c r="J18" s="14">
-        <v>19</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-42.105263157894</v>
-      </c>
-      <c r="L18" s="15">
-        <v>-42.105263157894</v>
-      </c>
-      <c r="M18" s="15">
-        <v>-57.692307692307</v>
-      </c>
       <c r="N18" s="15">
-        <v>-86.419753086419</v>
+        <v>-84.705882352941</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-41.176470588235</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
-        <v>-46.153846153846</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="I19" s="14">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="J19" s="14">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="K19" s="15">
-        <v>-25.663716814159</v>
+        <v>-24.21875</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.813559322033</v>
+        <v>-24.806201550387</v>
       </c>
       <c r="M19" s="15">
-        <v>-30.578512396694</v>
+        <v>-23.622047244094</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.098039215686</v>
+        <v>-41.916167664670</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
-      <c r="G20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>21</v>
+      <c r="G20" s="14">
+        <v>2</v>
+      </c>
+      <c r="H20" s="15">
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>3</v>
       </c>
       <c r="J20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="L20" s="15">
-        <v>-72.727272727272</v>
+        <v>-75</v>
       </c>
       <c r="M20" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.907216494845</v>
+        <v>-97.087378640776</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-40.909090909090</v>
+        <v>-28</v>
       </c>
       <c r="F21" s="17">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G21" s="17">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H21" s="18">
-        <v>-43.529411764705</v>
+        <v>-45.744680851063</v>
       </c>
       <c r="I21" s="17">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="J21" s="17">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="K21" s="18">
-        <v>-29.120879120879</v>
+        <v>-28.502415458937</v>
       </c>
       <c r="L21" s="18">
-        <v>-31.016042780748</v>
+        <v>-28.155339805825</v>
       </c>
       <c r="M21" s="18">
-        <v>-34.183673469387</v>
+        <v>-27.450980392156</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.148296593186</v>
+        <v>-72.592592592592</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,14 +1188,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="14">
         <v>2</v>
       </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
@@ -1224,31 +1224,31 @@
         <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
         <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
         <v>8</v>
       </c>
       <c r="J23" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K23" s="15">
-        <v>-27.272727272727</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M23" s="15">
         <v>14.285714285714</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>12.5</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F24" s="14">
         <v>64</v>
       </c>
       <c r="G24" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H24" s="15">
-        <v>39.130434782608</v>
+        <v>30.612244897959</v>
       </c>
       <c r="I24" s="14">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="J24" s="14">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="K24" s="15">
-        <v>16.417910447761</v>
+        <v>15.436241610738</v>
       </c>
       <c r="L24" s="15">
-        <v>45.794392523364</v>
+        <v>44.537815126050</v>
       </c>
       <c r="M24" s="15">
-        <v>14.705882352941</v>
+        <v>17.006802721088</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-61.538461538461</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G25" s="14">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H25" s="15">
-        <v>-21.621621621621</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="I25" s="14">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J25" s="14">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K25" s="15">
-        <v>21.621621621621</v>
+        <v>15.662650602409</v>
       </c>
       <c r="L25" s="15">
-        <v>83.673469387755</v>
+        <v>92</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>266.666666666667</v>
+        <v>75</v>
       </c>
       <c r="F26" s="14">
         <v>28</v>
       </c>
       <c r="G26" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H26" s="15">
-        <v>33.333333333333</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I26" s="14">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J26" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K26" s="15">
-        <v>48.837209302325</v>
+        <v>48.936170212766</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.538461538461</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
-        <v>16.363636363636</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
-      </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
@@ -1412,7 +1412,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>2</v>
+      </c>
+      <c r="G28" s="14">
+        <v>2</v>
+      </c>
+      <c r="H28" s="15">
         <v>0</v>
       </c>
-      <c r="F28" s="14">
-        <v>3</v>
-      </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-25</v>
-      </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
         <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="L28" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-71.428571428571</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K16" s="15">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-45.454545454545</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="M16" s="15">
-        <v>-25</v>
+        <v>-6.25</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.551181102362</v>
+        <v>-89.208633093525</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>1</v>
+      </c>
+      <c r="D17" s="14">
         <v>2</v>
       </c>
-      <c r="D17" s="14">
-        <v>1</v>
-      </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H17" s="15">
-        <v>-33.333333333333</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I17" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J17" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K17" s="15">
-        <v>-34.482758620689</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="L17" s="15">
         <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>-32.142857142857</v>
+        <v>-39.393939393939</v>
       </c>
       <c r="N17" s="15">
-        <v>-63.461538461538</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
+        <v>5</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="14">
         <v>3</v>
       </c>
-      <c r="E18" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F18" s="14">
-        <v>5</v>
-      </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-81.25</v>
       </c>
       <c r="I18" s="14">
         <v>13</v>
       </c>
       <c r="J18" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K18" s="15">
+        <v>-51.851851851851</v>
+      </c>
+      <c r="L18" s="15">
         <v>-40.909090909090</v>
       </c>
-      <c r="L18" s="15">
-        <v>-35</v>
-      </c>
       <c r="M18" s="15">
-        <v>-50</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.705882352941</v>
+        <v>-86.021505376344</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,54 +1057,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-13.333333333333</v>
+        <v>-31.25</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G19" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H19" s="15">
-        <v>-42.105263157894</v>
+        <v>-36.065573770491</v>
       </c>
       <c r="I19" s="14">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="J19" s="14">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="K19" s="15">
-        <v>-24.21875</v>
+        <v>-24.305555555555</v>
       </c>
       <c r="L19" s="15">
-        <v>-24.806201550387</v>
+        <v>-21.582733812949</v>
       </c>
       <c r="M19" s="15">
-        <v>-23.622047244094</v>
+        <v>-21.014492753623</v>
       </c>
       <c r="N19" s="15">
-        <v>-41.916167664670</v>
+        <v>-41.081081081081</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
@@ -1116,22 +1116,22 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="14">
         <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-75</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M20" s="15">
-        <v>-57.142857142857</v>
+        <v>-60</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.087378640776</v>
+        <v>-96.396396396396</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-28</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G21" s="17">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H21" s="18">
-        <v>-45.744680851063</v>
+        <v>-46</v>
       </c>
       <c r="I21" s="17">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="J21" s="17">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="K21" s="18">
-        <v>-28.502415458937</v>
+        <v>-29.787234042553</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.155339805825</v>
+        <v>-25.339366515837</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.450980392156</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.592592592592</v>
+        <v>-72.268907563025</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L22" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-38.461538461538</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>14.285714285714</v>
+        <v>25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>6.666666666666</v>
+        <v>21.052631578947</v>
       </c>
       <c r="F24" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H24" s="15">
-        <v>30.612244897959</v>
+        <v>26.785714285714</v>
       </c>
       <c r="I24" s="14">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="J24" s="14">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="K24" s="15">
-        <v>15.436241610738</v>
+        <v>15.476190476190</v>
       </c>
       <c r="L24" s="15">
-        <v>44.537815126050</v>
+        <v>50.387596899224</v>
       </c>
       <c r="M24" s="15">
-        <v>17.006802721088</v>
+        <v>20.496894409937</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="F25" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G25" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H25" s="15">
-        <v>-31.428571428571</v>
+        <v>-35</v>
       </c>
       <c r="I25" s="14">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="J25" s="14">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K25" s="15">
-        <v>15.662650602409</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L25" s="15">
-        <v>92</v>
+        <v>101.923076923077</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>75</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
         <v>18</v>
       </c>
       <c r="H26" s="15">
-        <v>55.555555555555</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J26" s="14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K26" s="15">
-        <v>48.936170212766</v>
+        <v>41.509433962264</v>
       </c>
       <c r="L26" s="15">
         <v>0</v>
       </c>
       <c r="M26" s="15">
-        <v>16.666666666666</v>
+        <v>13.636363636363</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I27" s="14">
+        <v>5</v>
+      </c>
+      <c r="J27" s="14">
+        <v>5</v>
+      </c>
+      <c r="K27" s="15">
         <v>0</v>
       </c>
-      <c r="I27" s="14">
-        <v>4</v>
-      </c>
-      <c r="J27" s="14">
-        <v>3</v>
-      </c>
-      <c r="K27" s="15">
-        <v>33.333333333333</v>
-      </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>10</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>-9.090909090909</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1496,8 +1496,8 @@
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+      <c r="M29" s="15">
+        <v>-100</v>
       </c>
       <c r="N29" s="15">
         <v>-100</v>
@@ -1537,8 +1537,8 @@
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+      <c r="M30" s="15">
+        <v>-100</v>
       </c>
       <c r="N30" s="15">
         <v>-100</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -896,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
@@ -905,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -914,16 +914,16 @@
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+      <c r="M15" s="15">
+        <v>300</v>
       </c>
       <c r="N15" s="15">
         <v>-42.857142857142</v>
@@ -933,14 +933,14 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>3</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
         <v>5</v>
@@ -955,19 +955,19 @@
         <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>-37.5</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="L16" s="15">
         <v>-31.818181818181</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.25</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.208633093525</v>
+        <v>-89.795918367346</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G17" s="14">
         <v>9</v>
       </c>
       <c r="H17" s="15">
-        <v>-44.444444444444</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I17" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J17" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K17" s="15">
-        <v>-35.483870967741</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>9.523809523809</v>
       </c>
       <c r="M17" s="15">
-        <v>-39.393939393939</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="N17" s="15">
-        <v>-66.666666666666</v>
+        <v>-63.492063492063</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-81.25</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>-51.851851851851</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="15">
-        <v>-40.909090909090</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M18" s="15">
-        <v>-53.571428571428</v>
+        <v>-50</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.021505376344</v>
+        <v>-87.155963302752</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,45 +1060,45 @@
         <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-31.25</v>
+        <v>10</v>
       </c>
       <c r="F19" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H19" s="15">
-        <v>-36.065573770491</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="I19" s="14">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="J19" s="14">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="K19" s="15">
-        <v>-24.305555555555</v>
+        <v>-22.077922077922</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.582733812949</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="M19" s="15">
-        <v>-21.014492753623</v>
+        <v>-17.808219178082</v>
       </c>
       <c r="N19" s="15">
-        <v>-41.081081081081</v>
+        <v>-42.583732057416</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1131,7 +1131,7 @@
         <v>-60</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.396396396396</v>
+        <v>-96.747967479674</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-42.857142857142</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H21" s="18">
-        <v>-46</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="J21" s="17">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="K21" s="18">
-        <v>-29.787234042553</v>
+        <v>-28.853754940711</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.339366515837</v>
+        <v>-25</v>
       </c>
       <c r="M21" s="18">
-        <v>-26.666666666666</v>
+        <v>-24.369747899159</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.268907563025</v>
+        <v>-72.644376899696</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -1198,19 +1198,19 @@
         <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K22" s="15">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-50</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M22" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
+        <v>11</v>
+      </c>
+      <c r="J23" s="14">
+        <v>16</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-31.25</v>
+      </c>
+      <c r="L23" s="15">
         <v>10</v>
       </c>
-      <c r="J23" s="14">
-        <v>14</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-28.571428571428</v>
-      </c>
-      <c r="L23" s="15">
+      <c r="M23" s="15">
         <v>0</v>
-      </c>
-      <c r="M23" s="15">
-        <v>25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>21.052631578947</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="F24" s="14">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G24" s="14">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H24" s="15">
-        <v>26.785714285714</v>
+        <v>2.941176470588</v>
       </c>
       <c r="I24" s="14">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="J24" s="14">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="K24" s="15">
-        <v>15.476190476190</v>
+        <v>11.290322580645</v>
       </c>
       <c r="L24" s="15">
-        <v>50.387596899224</v>
+        <v>47.857142857142</v>
       </c>
       <c r="M24" s="15">
-        <v>20.496894409937</v>
+        <v>13.114754098360</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G25" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H25" s="15">
-        <v>-35</v>
+        <v>-34.883720930232</v>
       </c>
       <c r="I25" s="14">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J25" s="14">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K25" s="15">
-        <v>7.142857142857</v>
+        <v>8.653846153846</v>
       </c>
       <c r="L25" s="15">
-        <v>101.923076923077</v>
+        <v>91.525423728813</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>6</v>
+      </c>
+      <c r="D26" s="14">
         <v>5</v>
       </c>
-      <c r="D26" s="14">
-        <v>6</v>
-      </c>
       <c r="E26" s="15">
-        <v>-16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G26" s="14">
         <v>18</v>
       </c>
       <c r="H26" s="15">
-        <v>66.666666666666</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I26" s="14">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J26" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K26" s="15">
-        <v>41.509433962264</v>
+        <v>39.655172413793</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M26" s="15">
-        <v>13.636363636363</v>
+        <v>6.578947368421</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="14">
         <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L27" s="15">
         <v>-16.666666666666</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>11.111111111111</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L28" s="15">
-        <v>-23.076923076923</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,20 +1551,20 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
@@ -1575,8 +1575,8 @@
       <c r="K31" s="15">
         <v>-50</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="15">
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -914,10 +914,10 @@
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
@@ -936,20 +936,20 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
         <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-44.444444444444</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I16" s="14">
         <v>15</v>
@@ -961,13 +961,13 @@
         <v>-42.307692307692</v>
       </c>
       <c r="L16" s="15">
-        <v>-31.818181818181</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="M16" s="15">
-        <v>-11.764705882352</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.795918367346</v>
+        <v>-90.506329113924</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
+        <v>200</v>
+      </c>
+      <c r="F17" s="14">
+        <v>10</v>
+      </c>
+      <c r="G17" s="14">
+        <v>8</v>
+      </c>
+      <c r="H17" s="15">
+        <v>25</v>
+      </c>
+      <c r="I17" s="14">
+        <v>27</v>
+      </c>
+      <c r="J17" s="14">
+        <v>36</v>
+      </c>
+      <c r="K17" s="15">
         <v>-25</v>
       </c>
-      <c r="F17" s="14">
-        <v>7</v>
-      </c>
-      <c r="G17" s="14">
-        <v>9</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-22.222222222222</v>
-      </c>
-      <c r="I17" s="14">
-        <v>23</v>
-      </c>
-      <c r="J17" s="14">
-        <v>35</v>
-      </c>
-      <c r="K17" s="15">
-        <v>-34.285714285714</v>
-      </c>
       <c r="L17" s="15">
-        <v>9.523809523809</v>
+        <v>8</v>
       </c>
       <c r="M17" s="15">
-        <v>-36.111111111111</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="N17" s="15">
-        <v>-63.492063492063</v>
+        <v>-58.461538461538</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-63.636363636363</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I18" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J18" s="14">
         <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L18" s="15">
-        <v>-46.153846153846</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M18" s="15">
-        <v>-50</v>
+        <v>-48.387096774193</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.155963302752</v>
+        <v>-86.991869918699</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>10</v>
+      </c>
+      <c r="D19" s="14">
         <v>11</v>
       </c>
-      <c r="D19" s="14">
-        <v>10</v>
-      </c>
       <c r="E19" s="15">
-        <v>10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G19" s="14">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H19" s="15">
-        <v>-24.137931034482</v>
+        <v>-13.461538461538</v>
       </c>
       <c r="I19" s="14">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="J19" s="14">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="K19" s="15">
-        <v>-22.077922077922</v>
+        <v>-20.606060606060</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.568627450980</v>
+        <v>-22.941176470588</v>
       </c>
       <c r="M19" s="15">
-        <v>-17.808219178082</v>
+        <v>-14.379084967320</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.583732057416</v>
+        <v>-40.990990990991</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1116,22 +1116,22 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="14">
         <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L20" s="15">
-        <v>-71.428571428571</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>-60</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.747967479674</v>
+        <v>-96.428571428571</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.666666666666</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F21" s="17">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G21" s="17">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="H21" s="18">
-        <v>-33.333333333333</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="J21" s="17">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="K21" s="18">
-        <v>-28.853754940711</v>
+        <v>-25.563909774436</v>
       </c>
       <c r="L21" s="18">
-        <v>-25</v>
+        <v>-26.394052044609</v>
       </c>
       <c r="M21" s="18">
-        <v>-24.369747899159</v>
+        <v>-22.352941176470</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.644376899696</v>
+        <v>-72.307692307692</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
@@ -1192,22 +1192,22 @@
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="14">
         <v>6</v>
       </c>
       <c r="J22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="L22" s="15">
-        <v>-45.454545454545</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="15">
         <v>100</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
-      </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J23" s="14">
         <v>16</v>
       </c>
       <c r="K23" s="15">
-        <v>-31.25</v>
+        <v>-25</v>
       </c>
       <c r="L23" s="15">
-        <v>10</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>-27.777777777777</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H24" s="15">
-        <v>2.941176470588</v>
+        <v>-4.054054054054</v>
       </c>
       <c r="I24" s="14">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="J24" s="14">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="K24" s="15">
-        <v>11.290322580645</v>
+        <v>8.653846153846</v>
       </c>
       <c r="L24" s="15">
-        <v>47.857142857142</v>
+        <v>52.702702702702</v>
       </c>
       <c r="M24" s="15">
-        <v>13.114754098360</v>
+        <v>15.897435897435</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>33.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G25" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H25" s="15">
-        <v>-34.883720930232</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J25" s="14">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="K25" s="15">
-        <v>8.653846153846</v>
+        <v>7.758620689655</v>
       </c>
       <c r="L25" s="15">
-        <v>91.525423728813</v>
+        <v>92.307692307692</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="F26" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H26" s="15">
-        <v>55.555555555555</v>
+        <v>57.894736842105</v>
       </c>
       <c r="I26" s="14">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J26" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K26" s="15">
-        <v>39.655172413793</v>
+        <v>50</v>
       </c>
       <c r="L26" s="15">
-        <v>1.25</v>
+        <v>6.896551724137</v>
       </c>
       <c r="M26" s="15">
-        <v>6.578947368421</v>
+        <v>16.25</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1406,13 +1406,13 @@
         <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L27" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
+        <v>50</v>
+      </c>
+      <c r="I28" s="14">
+        <v>15</v>
+      </c>
+      <c r="J28" s="14">
+        <v>12</v>
+      </c>
+      <c r="K28" s="15">
         <v>25</v>
       </c>
-      <c r="I28" s="14">
-        <v>13</v>
-      </c>
-      <c r="J28" s="14">
-        <v>11</v>
-      </c>
-      <c r="K28" s="15">
-        <v>18.181818181818</v>
-      </c>
       <c r="L28" s="15">
-        <v>-27.777777777777</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,8 +1493,8 @@
       <c r="K29" s="15">
         <v>-100</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="15">
+        <v>-100</v>
       </c>
       <c r="M29" s="15">
         <v>-100</v>
@@ -1534,8 +1534,8 @@
       <c r="K30" s="15">
         <v>-100</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="15">
+        <v>-100</v>
       </c>
       <c r="M30" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -881,11 +881,11 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="14">
+        <v>-100</v>
+      </c>
+      <c r="N14" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,210 +895,210 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="15">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
         <v>-100</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="14">
+      <c r="I15" s="15">
         <v>4</v>
       </c>
-      <c r="H15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I15" s="14">
-        <v>4</v>
-      </c>
-      <c r="J15" s="14">
+      <c r="J15" s="15">
         <v>7</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="14">
         <v>-42.857142857142</v>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="14">
         <v>0</v>
       </c>
-      <c r="M15" s="15">
+      <c r="M15" s="14">
         <v>300</v>
       </c>
-      <c r="N15" s="15">
-        <v>-42.857142857142</v>
+      <c r="N15" s="14">
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="14">
+      <c r="C16" s="15">
+        <v>1</v>
+      </c>
+      <c r="D16" s="15">
+        <v>5</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-80</v>
+      </c>
+      <c r="F16" s="15">
         <v>4</v>
       </c>
-      <c r="G16" s="14">
-        <v>9</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-55.555555555555</v>
-      </c>
-      <c r="I16" s="14">
-        <v>15</v>
-      </c>
-      <c r="J16" s="14">
-        <v>26</v>
-      </c>
-      <c r="K16" s="15">
-        <v>-42.307692307692</v>
-      </c>
-      <c r="L16" s="15">
-        <v>-48.275862068965</v>
-      </c>
-      <c r="M16" s="15">
-        <v>-16.666666666666</v>
-      </c>
-      <c r="N16" s="15">
-        <v>-90.506329113924</v>
+      <c r="G16" s="15">
+        <v>10</v>
+      </c>
+      <c r="H16" s="14">
+        <v>-60</v>
+      </c>
+      <c r="I16" s="15">
+        <v>16</v>
+      </c>
+      <c r="J16" s="15">
+        <v>31</v>
+      </c>
+      <c r="K16" s="14">
+        <v>-48.387096774193</v>
+      </c>
+      <c r="L16" s="14">
+        <v>-48.387096774193</v>
+      </c>
+      <c r="M16" s="14">
+        <v>-20</v>
+      </c>
+      <c r="N16" s="14">
+        <v>-90.751445086705</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="15">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15">
         <v>3</v>
       </c>
-      <c r="D17" s="14">
-        <v>1</v>
-      </c>
-      <c r="E17" s="15">
-        <v>200</v>
-      </c>
-      <c r="F17" s="14">
+      <c r="E17" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F17" s="15">
+        <v>9</v>
+      </c>
+      <c r="G17" s="15">
         <v>10</v>
       </c>
-      <c r="G17" s="14">
-        <v>8</v>
-      </c>
-      <c r="H17" s="15">
-        <v>25</v>
-      </c>
-      <c r="I17" s="14">
-        <v>27</v>
-      </c>
-      <c r="J17" s="14">
-        <v>36</v>
-      </c>
-      <c r="K17" s="15">
-        <v>-25</v>
-      </c>
-      <c r="L17" s="15">
-        <v>8</v>
-      </c>
-      <c r="M17" s="15">
-        <v>-34.146341463414</v>
-      </c>
-      <c r="N17" s="15">
-        <v>-58.461538461538</v>
+      <c r="H17" s="14">
+        <v>-10</v>
+      </c>
+      <c r="I17" s="15">
+        <v>28</v>
+      </c>
+      <c r="J17" s="15">
+        <v>39</v>
+      </c>
+      <c r="K17" s="14">
+        <v>-28.205128205128</v>
+      </c>
+      <c r="L17" s="14">
+        <v>3.703703703703</v>
+      </c>
+      <c r="M17" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="N17" s="14">
+        <v>-59.420289855072</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="14">
+      <c r="C18" s="15">
+        <v>2</v>
+      </c>
+      <c r="D18" s="15">
+        <v>4</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F18" s="15">
         <v>5</v>
       </c>
-      <c r="G18" s="14">
-        <v>9</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-44.444444444444</v>
-      </c>
-      <c r="I18" s="14">
-        <v>16</v>
-      </c>
-      <c r="J18" s="14">
-        <v>28</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-42.857142857142</v>
-      </c>
-      <c r="L18" s="15">
-        <v>-38.461538461538</v>
-      </c>
-      <c r="M18" s="15">
-        <v>-48.387096774193</v>
-      </c>
-      <c r="N18" s="15">
-        <v>-86.991869918699</v>
+      <c r="G18" s="15">
+        <v>10</v>
+      </c>
+      <c r="H18" s="14">
+        <v>-50</v>
+      </c>
+      <c r="I18" s="15">
+        <v>18</v>
+      </c>
+      <c r="J18" s="15">
+        <v>32</v>
+      </c>
+      <c r="K18" s="14">
+        <v>-43.75</v>
+      </c>
+      <c r="L18" s="14">
+        <v>-30.769230769230</v>
+      </c>
+      <c r="M18" s="14">
+        <v>-43.75</v>
+      </c>
+      <c r="N18" s="14">
+        <v>-86.466165413533</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="15">
         <v>10</v>
       </c>
-      <c r="D19" s="14">
-        <v>11</v>
-      </c>
-      <c r="E19" s="15">
-        <v>-9.090909090909</v>
-      </c>
-      <c r="F19" s="14">
-        <v>45</v>
-      </c>
-      <c r="G19" s="14">
-        <v>52</v>
-      </c>
-      <c r="H19" s="15">
-        <v>-13.461538461538</v>
-      </c>
-      <c r="I19" s="14">
-        <v>131</v>
-      </c>
-      <c r="J19" s="14">
-        <v>165</v>
-      </c>
-      <c r="K19" s="15">
-        <v>-20.606060606060</v>
-      </c>
-      <c r="L19" s="15">
-        <v>-22.941176470588</v>
-      </c>
-      <c r="M19" s="15">
-        <v>-14.379084967320</v>
-      </c>
-      <c r="N19" s="15">
-        <v>-40.990990990991</v>
+      <c r="D19" s="15">
+        <v>9</v>
+      </c>
+      <c r="E19" s="14">
+        <v>11.111111111111</v>
+      </c>
+      <c r="F19" s="15">
+        <v>40</v>
+      </c>
+      <c r="G19" s="15">
+        <v>46</v>
+      </c>
+      <c r="H19" s="14">
+        <v>-13.043478260869</v>
+      </c>
+      <c r="I19" s="15">
+        <v>140</v>
+      </c>
+      <c r="J19" s="15">
+        <v>174</v>
+      </c>
+      <c r="K19" s="14">
+        <v>-19.540229885057</v>
+      </c>
+      <c r="L19" s="14">
+        <v>-24.324324324324</v>
+      </c>
+      <c r="M19" s="14">
+        <v>-17.159763313609</v>
+      </c>
+      <c r="N19" s="14">
+        <v>-39.393939393939</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1106,32 +1106,32 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="15">
         <v>2</v>
       </c>
-      <c r="G20" s="14">
-        <v>2</v>
-      </c>
-      <c r="H20" s="15">
-        <v>0</v>
-      </c>
-      <c r="I20" s="14">
+      <c r="G20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="15">
         <v>5</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="15">
         <v>4</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="14">
         <v>25</v>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="14">
         <v>-66.666666666666</v>
       </c>
-      <c r="M20" s="15">
-        <v>-54.545454545454</v>
-      </c>
-      <c r="N20" s="15">
-        <v>-96.428571428571</v>
+      <c r="M20" s="14">
+        <v>-64.285714285714</v>
+      </c>
+      <c r="N20" s="14">
+        <v>-96.732026143790</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,75 +1142,75 @@
         <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>7.692307692307</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G21" s="17">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.428571428571</v>
+        <v>-25</v>
       </c>
       <c r="I21" s="17">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="J21" s="17">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="K21" s="18">
-        <v>-25.563909774436</v>
+        <v>-26.480836236933</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.394052044609</v>
+        <v>-26.736111111111</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.352941176470</v>
+        <v>-24.372759856630</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.307692307692</v>
+        <v>-72.526041666666</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
-      <c r="G22" s="14">
+      <c r="C22" s="15">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
+        <v>3</v>
+      </c>
+      <c r="G22" s="15">
         <v>4</v>
       </c>
-      <c r="H22" s="15">
-        <v>-75</v>
-      </c>
-      <c r="I22" s="14">
-        <v>6</v>
-      </c>
-      <c r="J22" s="14">
+      <c r="H22" s="14">
+        <v>-25</v>
+      </c>
+      <c r="I22" s="15">
+        <v>8</v>
+      </c>
+      <c r="J22" s="15">
         <v>10</v>
       </c>
-      <c r="K22" s="15">
-        <v>-40</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-50</v>
-      </c>
-      <c r="M22" s="15">
-        <v>100</v>
+      <c r="K22" s="14">
+        <v>-20</v>
+      </c>
+      <c r="L22" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="M22" s="14">
+        <v>166.666666666667</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1229,29 +1229,29 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="15">
         <v>4</v>
       </c>
-      <c r="G23" s="14">
-        <v>5</v>
-      </c>
-      <c r="H23" s="15">
+      <c r="G23" s="15">
+        <v>3</v>
+      </c>
+      <c r="H23" s="14">
+        <v>33.333333333333</v>
+      </c>
+      <c r="I23" s="15">
+        <v>12</v>
+      </c>
+      <c r="J23" s="15">
+        <v>16</v>
+      </c>
+      <c r="K23" s="14">
+        <v>-25</v>
+      </c>
+      <c r="L23" s="14">
+        <v>9.090909090909</v>
+      </c>
+      <c r="M23" s="14">
         <v>-20</v>
-      </c>
-      <c r="I23" s="14">
-        <v>12</v>
-      </c>
-      <c r="J23" s="14">
-        <v>16</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-25</v>
-      </c>
-      <c r="L23" s="15">
-        <v>9.090909090909</v>
-      </c>
-      <c r="M23" s="15">
-        <v>-14.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="14">
-        <v>22</v>
-      </c>
-      <c r="D24" s="14">
-        <v>22</v>
-      </c>
-      <c r="E24" s="15">
-        <v>0</v>
-      </c>
-      <c r="F24" s="14">
-        <v>71</v>
-      </c>
-      <c r="G24" s="14">
-        <v>74</v>
-      </c>
-      <c r="H24" s="15">
-        <v>-4.054054054054</v>
-      </c>
-      <c r="I24" s="14">
-        <v>226</v>
-      </c>
-      <c r="J24" s="14">
-        <v>208</v>
-      </c>
-      <c r="K24" s="15">
-        <v>8.653846153846</v>
-      </c>
-      <c r="L24" s="15">
-        <v>52.702702702702</v>
-      </c>
-      <c r="M24" s="15">
-        <v>15.897435897435</v>
+      <c r="C24" s="15">
+        <v>20</v>
+      </c>
+      <c r="D24" s="15">
+        <v>21</v>
+      </c>
+      <c r="E24" s="14">
+        <v>-4.761904761904</v>
+      </c>
+      <c r="F24" s="15">
+        <v>77</v>
+      </c>
+      <c r="G24" s="15">
+        <v>80</v>
+      </c>
+      <c r="H24" s="14">
+        <v>-3.75</v>
+      </c>
+      <c r="I24" s="15">
+        <v>246</v>
+      </c>
+      <c r="J24" s="15">
+        <v>229</v>
+      </c>
+      <c r="K24" s="14">
+        <v>7.423580786026</v>
+      </c>
+      <c r="L24" s="14">
+        <v>52.795031055900</v>
+      </c>
+      <c r="M24" s="14">
+        <v>14.953271028037</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>14</v>
-      </c>
-      <c r="D25" s="14">
-        <v>12</v>
-      </c>
-      <c r="E25" s="15">
-        <v>16.666666666666</v>
-      </c>
-      <c r="F25" s="14">
-        <v>35</v>
-      </c>
-      <c r="G25" s="14">
-        <v>42</v>
-      </c>
-      <c r="H25" s="15">
-        <v>-16.666666666666</v>
-      </c>
-      <c r="I25" s="14">
-        <v>125</v>
-      </c>
-      <c r="J25" s="14">
-        <v>116</v>
-      </c>
-      <c r="K25" s="15">
-        <v>7.758620689655</v>
-      </c>
-      <c r="L25" s="15">
-        <v>92.307692307692</v>
+      <c r="C25" s="15">
+        <v>10</v>
+      </c>
+      <c r="D25" s="15">
+        <v>15</v>
+      </c>
+      <c r="E25" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F25" s="15">
+        <v>39</v>
+      </c>
+      <c r="G25" s="15">
+        <v>48</v>
+      </c>
+      <c r="H25" s="14">
+        <v>-18.75</v>
+      </c>
+      <c r="I25" s="15">
+        <v>135</v>
+      </c>
+      <c r="J25" s="15">
+        <v>131</v>
+      </c>
+      <c r="K25" s="14">
+        <v>3.053435114503</v>
+      </c>
+      <c r="L25" s="14">
+        <v>82.432432432432</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="14">
-        <v>12</v>
-      </c>
-      <c r="D26" s="14">
-        <v>4</v>
-      </c>
-      <c r="E26" s="15">
-        <v>200</v>
-      </c>
-      <c r="F26" s="14">
-        <v>30</v>
-      </c>
-      <c r="G26" s="14">
-        <v>19</v>
-      </c>
-      <c r="H26" s="15">
-        <v>57.894736842105</v>
-      </c>
-      <c r="I26" s="14">
-        <v>93</v>
-      </c>
-      <c r="J26" s="14">
-        <v>62</v>
-      </c>
-      <c r="K26" s="15">
-        <v>50</v>
-      </c>
-      <c r="L26" s="15">
-        <v>6.896551724137</v>
-      </c>
-      <c r="M26" s="15">
-        <v>16.25</v>
+      <c r="C26" s="15">
+        <v>5</v>
+      </c>
+      <c r="D26" s="15">
+        <v>8</v>
+      </c>
+      <c r="E26" s="14">
+        <v>-37.5</v>
+      </c>
+      <c r="F26" s="15">
+        <v>28</v>
+      </c>
+      <c r="G26" s="15">
+        <v>23</v>
+      </c>
+      <c r="H26" s="14">
+        <v>21.739130434782</v>
+      </c>
+      <c r="I26" s="15">
+        <v>98</v>
+      </c>
+      <c r="J26" s="15">
+        <v>70</v>
+      </c>
+      <c r="K26" s="14">
+        <v>40</v>
+      </c>
+      <c r="L26" s="14">
+        <v>11.363636363636</v>
+      </c>
+      <c r="M26" s="14">
+        <v>18.072289156626</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
-      </c>
-      <c r="G27" s="14">
+      <c r="G27" s="15">
         <v>4</v>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="14">
         <v>-75</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="15">
         <v>5</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="15">
         <v>7</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="14">
         <v>-28.571428571428</v>
       </c>
-      <c r="L27" s="15">
-        <v>-28.571428571428</v>
+      <c r="L27" s="14">
+        <v>-37.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,34 +1425,34 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="E28" s="15">
-        <v>100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>6</v>
-      </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
-      <c r="H28" s="15">
-        <v>50</v>
-      </c>
-      <c r="I28" s="14">
+      <c r="E28" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="15">
+        <v>5</v>
+      </c>
+      <c r="G28" s="15">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
+      <c r="I28" s="15">
         <v>15</v>
       </c>
-      <c r="J28" s="14">
-        <v>12</v>
-      </c>
-      <c r="K28" s="15">
-        <v>25</v>
-      </c>
-      <c r="L28" s="15">
+      <c r="J28" s="15">
+        <v>13</v>
+      </c>
+      <c r="K28" s="14">
+        <v>15.384615384615</v>
+      </c>
+      <c r="L28" s="14">
         <v>-16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
@@ -1487,19 +1487,19 @@
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="15">
         <v>1</v>
       </c>
-      <c r="K29" s="15">
+      <c r="K29" s="14">
         <v>-100</v>
       </c>
-      <c r="L29" s="15">
+      <c r="L29" s="14">
         <v>-100</v>
       </c>
-      <c r="M29" s="15">
+      <c r="M29" s="14">
         <v>-100</v>
       </c>
-      <c r="N29" s="15">
+      <c r="N29" s="14">
         <v>-100</v>
       </c>
     </row>
@@ -1528,19 +1528,19 @@
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="15">
         <v>1</v>
       </c>
-      <c r="K30" s="15">
+      <c r="K30" s="14">
         <v>-100</v>
       </c>
-      <c r="L30" s="15">
+      <c r="L30" s="14">
         <v>-100</v>
       </c>
-      <c r="M30" s="15">
+      <c r="M30" s="14">
         <v>-100</v>
       </c>
-      <c r="N30" s="15">
+      <c r="N30" s="14">
         <v>-100</v>
       </c>
     </row>
@@ -1560,22 +1560,22 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="15">
         <v>1</v>
       </c>
-      <c r="H31" s="15">
+      <c r="H31" s="14">
         <v>-100</v>
       </c>
-      <c r="I31" s="14">
+      <c r="I31" s="15">
         <v>1</v>
       </c>
-      <c r="J31" s="14">
+      <c r="J31" s="15">
         <v>2</v>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="14">
         <v>-50</v>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="14">
         <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="15">
         <v>6</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="15">
         <v>8</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="15">
         <v>4</v>
       </c>
-      <c r="I39" s="14">
+      <c r="I39" s="15">
         <v>3</v>
       </c>
-      <c r="J39" s="14">
+      <c r="J39" s="15">
         <v>1</v>
       </c>
-      <c r="K39" s="15">
+      <c r="K39" s="14">
         <v>-66.666666666666</v>
       </c>
-      <c r="L39" s="15">
+      <c r="L39" s="14">
         <v>-75</v>
       </c>
-      <c r="M39" s="15">
+      <c r="M39" s="14">
         <v>-87.5</v>
       </c>
-      <c r="N39" s="15">
+      <c r="N39" s="14">
         <v>-83.333333333333</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="15">
         <v>23</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="15">
         <v>27</v>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="15">
         <v>12</v>
       </c>
-      <c r="I40" s="14">
+      <c r="I40" s="15">
         <v>5</v>
       </c>
-      <c r="J40" s="14">
+      <c r="J40" s="15">
         <v>16</v>
       </c>
-      <c r="K40" s="15">
+      <c r="K40" s="14">
         <v>220</v>
       </c>
-      <c r="L40" s="15">
+      <c r="L40" s="14">
         <v>33.333333333333</v>
       </c>
-      <c r="M40" s="15">
+      <c r="M40" s="14">
         <v>-40.740740740740</v>
       </c>
-      <c r="N40" s="15">
+      <c r="N40" s="14">
         <v>-30.434782608695</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="15">
         <v>761</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="15">
         <v>617</v>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="15">
         <v>272</v>
       </c>
-      <c r="I41" s="14">
+      <c r="I41" s="15">
         <v>135</v>
       </c>
-      <c r="J41" s="14">
+      <c r="J41" s="15">
         <v>110</v>
       </c>
-      <c r="K41" s="15">
+      <c r="K41" s="14">
         <v>-18.518518518518</v>
       </c>
-      <c r="L41" s="15">
+      <c r="L41" s="14">
         <v>-59.558823529411</v>
       </c>
-      <c r="M41" s="15">
+      <c r="M41" s="14">
         <v>-82.171799027552</v>
       </c>
-      <c r="N41" s="15">
+      <c r="N41" s="14">
         <v>-85.545335085413</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="15">
         <v>301</v>
       </c>
-      <c r="E42" s="14">
+      <c r="E42" s="15">
         <v>249</v>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="15">
         <v>197</v>
       </c>
-      <c r="I42" s="14">
+      <c r="I42" s="15">
         <v>103</v>
       </c>
-      <c r="J42" s="14">
+      <c r="J42" s="15">
         <v>156</v>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="14">
         <v>51.456310679611</v>
       </c>
-      <c r="L42" s="15">
+      <c r="L42" s="14">
         <v>-20.812182741116</v>
       </c>
-      <c r="M42" s="15">
+      <c r="M42" s="14">
         <v>-37.349397590361</v>
       </c>
-      <c r="N42" s="15">
+      <c r="N42" s="14">
         <v>-48.172757475083</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="15">
         <v>865</v>
       </c>
-      <c r="E43" s="14">
+      <c r="E43" s="15">
         <v>639</v>
       </c>
-      <c r="G43" s="14">
+      <c r="G43" s="15">
         <v>298</v>
       </c>
-      <c r="I43" s="14">
+      <c r="I43" s="15">
         <v>108</v>
       </c>
-      <c r="J43" s="14">
+      <c r="J43" s="15">
         <v>100</v>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="14">
         <v>-7.407407407407</v>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="14">
         <v>-66.442953020134</v>
       </c>
-      <c r="M43" s="15">
+      <c r="M43" s="14">
         <v>-84.350547730829</v>
       </c>
-      <c r="N43" s="15">
+      <c r="N43" s="14">
         <v>-88.439306358381</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="15">
         <v>1156</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="15">
         <v>828</v>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="15">
         <v>576</v>
       </c>
-      <c r="I44" s="14">
+      <c r="I44" s="15">
         <v>447</v>
       </c>
-      <c r="J44" s="14">
+      <c r="J44" s="15">
         <v>626</v>
       </c>
-      <c r="K44" s="15">
+      <c r="K44" s="14">
         <v>40.044742729306</v>
       </c>
-      <c r="L44" s="15">
+      <c r="L44" s="14">
         <v>8.680555555555</v>
       </c>
-      <c r="M44" s="15">
+      <c r="M44" s="14">
         <v>-24.396135265700</v>
       </c>
-      <c r="N44" s="15">
+      <c r="N44" s="14">
         <v>-45.847750865051</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="15">
         <v>1039</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="15">
         <v>512</v>
       </c>
-      <c r="G45" s="14">
+      <c r="G45" s="15">
         <v>312</v>
       </c>
-      <c r="I45" s="14">
+      <c r="I45" s="15">
         <v>127</v>
       </c>
-      <c r="J45" s="14">
+      <c r="J45" s="15">
         <v>35</v>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="14">
         <v>-72.440944881889</v>
       </c>
-      <c r="L45" s="15">
+      <c r="L45" s="14">
         <v>-88.782051282051</v>
       </c>
-      <c r="M45" s="15">
+      <c r="M45" s="14">
         <v>-93.1640625</v>
       </c>
-      <c r="N45" s="15">
+      <c r="N45" s="14">
         <v>-96.631376323387</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -905,28 +905,28 @@
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
       </c>
       <c r="I15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="15">
         <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M15" s="14">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="N15" s="14">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
-      </c>
-      <c r="D16" s="15">
-        <v>5</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-80</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>-60</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I16" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" s="15">
         <v>31</v>
       </c>
       <c r="K16" s="14">
-        <v>-48.387096774193</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="L16" s="14">
-        <v>-48.387096774193</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M16" s="14">
-        <v>-20</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N16" s="14">
-        <v>-90.751445086705</v>
+        <v>-90.322580645161</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-66.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G17" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H17" s="14">
-        <v>-10</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I17" s="15">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J17" s="15">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K17" s="14">
-        <v>-28.205128205128</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L17" s="14">
-        <v>3.703703703703</v>
+        <v>3.125</v>
       </c>
       <c r="M17" s="14">
-        <v>-33.333333333333</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="N17" s="14">
-        <v>-59.420289855072</v>
+        <v>-54.794520547945</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H18" s="14">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
       <c r="I18" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J18" s="15">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K18" s="14">
-        <v>-43.75</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="L18" s="14">
-        <v>-30.769230769230</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M18" s="14">
-        <v>-43.75</v>
+        <v>-31.25</v>
       </c>
       <c r="N18" s="14">
-        <v>-86.466165413533</v>
+        <v>-84.172661870503</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" s="14">
-        <v>11.111111111111</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G19" s="15">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H19" s="14">
-        <v>-13.043478260869</v>
+        <v>4.761904761904</v>
       </c>
       <c r="I19" s="15">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="J19" s="15">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="K19" s="14">
-        <v>-19.540229885057</v>
+        <v>-17.204301075268</v>
       </c>
       <c r="L19" s="14">
-        <v>-24.324324324324</v>
+        <v>-21.025641025641</v>
       </c>
       <c r="M19" s="14">
-        <v>-17.159763313609</v>
+        <v>-12</v>
       </c>
       <c r="N19" s="14">
-        <v>-39.393939393939</v>
+        <v>-38.888888888888</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,7 +1107,7 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1125,13 +1125,13 @@
         <v>25</v>
       </c>
       <c r="L20" s="14">
+        <v>-70.588235294117</v>
+      </c>
+      <c r="M20" s="14">
         <v>-66.666666666666</v>
       </c>
-      <c r="M20" s="14">
-        <v>-64.285714285714</v>
-      </c>
       <c r="N20" s="14">
-        <v>-96.732026143790</v>
+        <v>-97.142857142857</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
         <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G21" s="17">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>-25</v>
+        <v>-8.219178082191</v>
       </c>
       <c r="I21" s="17">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="J21" s="17">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.480836236933</v>
+        <v>-23.051948051948</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.736111111111</v>
+        <v>-23.300970873786</v>
       </c>
       <c r="M21" s="18">
-        <v>-24.372759856630</v>
+        <v>-18.275862068965</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.526041666666</v>
+        <v>-71.582733812949</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
         <v>2</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
+      <c r="G22" s="15">
         <v>3</v>
       </c>
-      <c r="G22" s="15">
-        <v>4</v>
-      </c>
       <c r="H22" s="14">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="15">
         <v>8</v>
@@ -1220,14 +1220,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="15">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
       </c>
       <c r="F23" s="15">
         <v>4</v>
@@ -1239,19 +1239,19 @@
         <v>33.333333333333</v>
       </c>
       <c r="I23" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J23" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K23" s="14">
-        <v>-25</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="L23" s="14">
-        <v>9.090909090909</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M23" s="14">
-        <v>-20</v>
+        <v>-18.75</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E24" s="14">
-        <v>-4.761904761904</v>
+        <v>38.888888888888</v>
       </c>
       <c r="F24" s="15">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G24" s="15">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H24" s="14">
-        <v>-3.75</v>
+        <v>0</v>
       </c>
       <c r="I24" s="15">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="J24" s="15">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="K24" s="14">
-        <v>7.423580786026</v>
+        <v>9.311740890688</v>
       </c>
       <c r="L24" s="14">
-        <v>52.795031055900</v>
+        <v>51.685393258427</v>
       </c>
       <c r="M24" s="14">
-        <v>14.953271028037</v>
+        <v>16.379310344827</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D25" s="15">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>-33.333333333333</v>
+        <v>260</v>
       </c>
       <c r="F25" s="15">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G25" s="15">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H25" s="14">
-        <v>-18.75</v>
+        <v>28.947368421052</v>
       </c>
       <c r="I25" s="15">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="J25" s="15">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K25" s="14">
-        <v>3.053435114503</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L25" s="14">
-        <v>82.432432432432</v>
+        <v>94.871794871794</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>-37.5</v>
+        <v>250</v>
       </c>
       <c r="F26" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G26" s="15">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H26" s="14">
-        <v>21.739130434782</v>
+        <v>57.894736842105</v>
       </c>
       <c r="I26" s="15">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="J26" s="15">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K26" s="14">
-        <v>40</v>
+        <v>45.833333333333</v>
       </c>
       <c r="L26" s="14">
-        <v>11.363636363636</v>
+        <v>10.526315789473</v>
       </c>
       <c r="M26" s="14">
-        <v>18.072289156626</v>
+        <v>8.247422680412</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="15">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="15">
         <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L27" s="14">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I28" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" s="15">
         <v>13</v>
       </c>
       <c r="K28" s="14">
-        <v>15.384615384615</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L28" s="14">
-        <v>-16.666666666666</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -914,10 +914,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="14">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="L15" s="14">
         <v>25</v>
@@ -936,38 +936,38 @@
       <c r="C16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
         <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>-57.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I16" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K16" s="14">
-        <v>-41.935483870967</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="L16" s="14">
-        <v>-45.454545454545</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="M16" s="14">
-        <v>-18.181818181818</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="N16" s="14">
-        <v>-90.322580645161</v>
+        <v>-90.206185567010</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
-      </c>
-      <c r="D17" s="15">
-        <v>6</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-16.666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H17" s="14">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J17" s="15">
         <v>45</v>
       </c>
       <c r="K17" s="14">
-        <v>-26.666666666666</v>
+        <v>-24.444444444444</v>
       </c>
       <c r="L17" s="14">
-        <v>3.125</v>
+        <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>-23.255813953488</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="N17" s="14">
-        <v>-54.794520547945</v>
+        <v>-54.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
         <v>3</v>
       </c>
       <c r="E18" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F18" s="15">
+        <v>10</v>
+      </c>
+      <c r="G18" s="15">
+        <v>10</v>
+      </c>
+      <c r="H18" s="14">
         <v>0</v>
       </c>
-      <c r="F18" s="15">
-        <v>7</v>
-      </c>
-      <c r="G18" s="15">
-        <v>8</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-12.5</v>
-      </c>
       <c r="I18" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J18" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K18" s="14">
-        <v>-37.142857142857</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="L18" s="14">
-        <v>-21.428571428571</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-31.25</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="N18" s="14">
-        <v>-84.172661870503</v>
+        <v>-83.225806451612</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>16.666666666666</v>
+        <v>62.5</v>
       </c>
       <c r="F19" s="15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G19" s="15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H19" s="14">
-        <v>4.761904761904</v>
+        <v>20</v>
       </c>
       <c r="I19" s="15">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="J19" s="15">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K19" s="14">
-        <v>-17.204301075268</v>
+        <v>-13.402061855670</v>
       </c>
       <c r="L19" s="14">
-        <v>-21.025641025641</v>
+        <v>-20.754716981132</v>
       </c>
       <c r="M19" s="14">
-        <v>-12</v>
+        <v>-10.160427807486</v>
       </c>
       <c r="N19" s="14">
-        <v>-38.888888888888</v>
+        <v>-36.603773584905</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>1</v>
       </c>
-      <c r="G20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>21</v>
+      <c r="G20" s="15">
+        <v>2</v>
+      </c>
+      <c r="H20" s="14">
+        <v>-50</v>
       </c>
       <c r="I20" s="15">
         <v>5</v>
       </c>
       <c r="J20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K20" s="14">
-        <v>25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L20" s="14">
         <v>-70.588235294117</v>
       </c>
       <c r="M20" s="14">
-        <v>-66.666666666666</v>
+        <v>-68.75</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.142857142857</v>
+        <v>-97.267759562841</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.219178082191</v>
+        <v>2.816901408450</v>
       </c>
       <c r="I21" s="17">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="J21" s="17">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.051948051948</v>
+        <v>-20.679012345679</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.300970873786</v>
+        <v>-22.590361445783</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.275862068965</v>
+        <v>-17.096774193548</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.582733812949</v>
+        <v>-70.828603859250</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,10 +1192,10 @@
         <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I22" s="15">
         <v>8</v>
@@ -1220,23 +1220,23 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="15">
+        <v>2</v>
+      </c>
+      <c r="G23" s="15">
         <v>1</v>
       </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>0</v>
-      </c>
-      <c r="F23" s="15">
-        <v>4</v>
-      </c>
-      <c r="G23" s="15">
-        <v>3</v>
-      </c>
       <c r="H23" s="14">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I23" s="15">
         <v>13</v>
@@ -1248,10 +1248,10 @@
         <v>-23.529411764705</v>
       </c>
       <c r="L23" s="14">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M23" s="14">
-        <v>-18.75</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E24" s="14">
-        <v>38.888888888888</v>
+        <v>-10</v>
       </c>
       <c r="F24" s="15">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G24" s="15">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H24" s="14">
         <v>0</v>
       </c>
       <c r="I24" s="15">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="J24" s="15">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="K24" s="14">
-        <v>9.311740890688</v>
+        <v>6.741573033707</v>
       </c>
       <c r="L24" s="14">
-        <v>51.685393258427</v>
+        <v>50</v>
       </c>
       <c r="M24" s="14">
-        <v>16.379310344827</v>
+        <v>13.545816733067</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>260</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F25" s="15">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G25" s="15">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H25" s="14">
-        <v>28.947368421052</v>
+        <v>6.976744186046</v>
       </c>
       <c r="I25" s="15">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J25" s="15">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="K25" s="14">
-        <v>11.764705882352</v>
+        <v>6.802721088435</v>
       </c>
       <c r="L25" s="14">
-        <v>94.871794871794</v>
+        <v>89.156626506024</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>250</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="15">
         <v>30</v>
       </c>
       <c r="G26" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H26" s="14">
-        <v>57.894736842105</v>
+        <v>30.434782608695</v>
       </c>
       <c r="I26" s="15">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J26" s="15">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="K26" s="14">
-        <v>45.833333333333</v>
+        <v>37.037037037037</v>
       </c>
       <c r="L26" s="14">
-        <v>10.526315789473</v>
+        <v>7.766990291262</v>
       </c>
       <c r="M26" s="14">
-        <v>8.247422680412</v>
+        <v>-0.892857142857</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1406,10 +1406,10 @@
         <v>6</v>
       </c>
       <c r="J27" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="14">
         <v>-33.333333333333</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>23.076923076923</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L28" s="14">
-        <v>-11.111111111111</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="15">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="15">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="15">
-        <v>2</v>
-      </c>
       <c r="H15" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J15" s="15">
         <v>8</v>
       </c>
       <c r="K15" s="14">
-        <v>-37.5</v>
+        <v>-12.5</v>
       </c>
       <c r="L15" s="14">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M15" s="14">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="N15" s="14">
-        <v>-37.5</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H16" s="14">
-        <v>-42.857142857142</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J16" s="15">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K16" s="14">
-        <v>-42.424242424242</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="L16" s="14">
-        <v>-45.714285714285</v>
+        <v>-37.837837837837</v>
       </c>
       <c r="M16" s="14">
-        <v>-17.391304347826</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="N16" s="14">
-        <v>-90.206185567010</v>
+        <v>-88.834951456310</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -977,38 +977,38 @@
       <c r="C17" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="D17" s="15">
+        <v>6</v>
+      </c>
+      <c r="E17" s="14">
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I17" s="15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J17" s="15">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K17" s="14">
-        <v>-24.444444444444</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L17" s="14">
         <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>-29.166666666666</v>
+        <v>-25</v>
       </c>
       <c r="N17" s="14">
-        <v>-54.666666666666</v>
+        <v>-54.430379746835</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
         <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I18" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J18" s="15">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K18" s="14">
-        <v>-31.578947368421</v>
+        <v>-31.707317073170</v>
       </c>
       <c r="L18" s="14">
-        <v>-13.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="M18" s="14">
-        <v>-21.212121212121</v>
+        <v>-20</v>
       </c>
       <c r="N18" s="14">
-        <v>-83.225806451612</v>
+        <v>-82.926829268292</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
         <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>62.5</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="15">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G19" s="15">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H19" s="14">
-        <v>20</v>
+        <v>18.918918918918</v>
       </c>
       <c r="I19" s="15">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="J19" s="15">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="K19" s="14">
-        <v>-13.402061855670</v>
+        <v>-13.861386138613</v>
       </c>
       <c r="L19" s="14">
-        <v>-20.754716981132</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="M19" s="14">
-        <v>-10.160427807486</v>
+        <v>-9.844559585492</v>
       </c>
       <c r="N19" s="14">
-        <v>-36.603773584905</v>
+        <v>-36.956521739130</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,20 +1100,20 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="15">
-        <v>1</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="15">
         <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="15">
         <v>5</v>
@@ -1125,13 +1125,13 @@
         <v>-16.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>-70.588235294117</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="M20" s="14">
         <v>-68.75</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.267759562841</v>
+        <v>-97.326203208556</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>12.5</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H21" s="18">
-        <v>2.816901408450</v>
+        <v>-11.25</v>
       </c>
       <c r="I21" s="17">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="J21" s="17">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.679012345679</v>
+        <v>-21.098265895953</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.590361445783</v>
+        <v>-23.098591549295</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.096774193548</v>
+        <v>-15.479876160990</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.828603859250</v>
+        <v>-70.358306188925</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
-      </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="15">
         <v>10</v>
       </c>
       <c r="K22" s="14">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="L22" s="14">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="M22" s="14">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>2</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I23" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J23" s="15">
         <v>17</v>
       </c>
       <c r="K23" s="14">
-        <v>-23.529411764705</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L23" s="14">
-        <v>0</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M23" s="14">
-        <v>-23.529411764705</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" s="15">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E24" s="14">
-        <v>-10</v>
+        <v>35.714285714285</v>
       </c>
       <c r="F24" s="15">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G24" s="15">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H24" s="14">
-        <v>0</v>
+        <v>13.698630136986</v>
       </c>
       <c r="I24" s="15">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="J24" s="15">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="K24" s="14">
-        <v>6.741573033707</v>
+        <v>8.540925266903</v>
       </c>
       <c r="L24" s="14">
-        <v>50</v>
+        <v>51.741293532338</v>
       </c>
       <c r="M24" s="14">
-        <v>13.545816733067</v>
+        <v>14.232209737827</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25" s="14">
-        <v>-27.272727272727</v>
+        <v>-10</v>
       </c>
       <c r="F25" s="15">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G25" s="15">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H25" s="14">
-        <v>6.976744186046</v>
+        <v>9.756097560975</v>
       </c>
       <c r="I25" s="15">
+        <v>166</v>
+      </c>
+      <c r="J25" s="15">
         <v>157</v>
       </c>
-      <c r="J25" s="15">
-        <v>147</v>
-      </c>
       <c r="K25" s="14">
-        <v>6.802721088435</v>
+        <v>5.732484076433</v>
       </c>
       <c r="L25" s="14">
-        <v>89.156626506024</v>
+        <v>86.516853932584</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>-33.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F26" s="15">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G26" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H26" s="14">
-        <v>30.434782608695</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I26" s="15">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J26" s="15">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K26" s="14">
-        <v>37.037037037037</v>
+        <v>28.409090909090</v>
       </c>
       <c r="L26" s="14">
-        <v>7.766990291262</v>
+        <v>6.603773584905</v>
       </c>
       <c r="M26" s="14">
-        <v>-0.892857142857</v>
+        <v>-5.042016806722</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="15">
+        <v>2</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
       </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
       <c r="H27" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" s="15">
         <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L27" s="14">
-        <v>-33.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="I28" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J28" s="15">
         <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>21.428571428571</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L28" s="14">
-        <v>-10.526315789473</v>
+        <v>5.263157894736</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="15">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="15">
         <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L31" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-010pct.xlsx
+++ b/data/source/weekly/cs-en-us-010pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -892,35 +892,35 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>2</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>7</v>
       </c>
       <c r="J15" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="14">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L15" s="14">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="M15" s="14">
         <v>250</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
-      </c>
-      <c r="D16" s="15">
-        <v>5</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-20</v>
+        <v>3</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>-33.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I16" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J16" s="15">
         <v>38</v>
       </c>
       <c r="K16" s="14">
-        <v>-39.473684210526</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="L16" s="14">
-        <v>-37.837837837837</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="M16" s="14">
-        <v>-17.857142857142</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.834951456310</v>
+        <v>-88.181818181818</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>-66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" s="14">
-        <v>-40</v>
+        <v>-31.25</v>
       </c>
       <c r="I17" s="15">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J17" s="15">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K17" s="14">
-        <v>-29.411764705882</v>
+        <v>-29.090909090909</v>
       </c>
       <c r="L17" s="14">
-        <v>0</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="M17" s="14">
-        <v>-25</v>
+        <v>-20.408163265306</v>
       </c>
       <c r="N17" s="14">
-        <v>-54.430379746835</v>
+        <v>-54.117647058823</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
-      </c>
-      <c r="D18" s="15">
-        <v>3</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>-38.461538461538</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I18" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J18" s="15">
         <v>41</v>
       </c>
       <c r="K18" s="14">
-        <v>-31.707317073170</v>
+        <v>-29.268292682926</v>
       </c>
       <c r="L18" s="14">
-        <v>-12.5</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="M18" s="14">
-        <v>-20</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="N18" s="14">
-        <v>-82.926829268292</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E19" s="14">
-        <v>-25</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G19" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H19" s="14">
-        <v>18.918918918918</v>
+        <v>15</v>
       </c>
       <c r="I19" s="15">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="J19" s="15">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="K19" s="14">
-        <v>-13.861386138613</v>
+        <v>-12.616822429906</v>
       </c>
       <c r="L19" s="14">
-        <v>-23.684210526315</v>
+        <v>-21.757322175732</v>
       </c>
       <c r="M19" s="14">
-        <v>-9.844559585492</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N19" s="14">
-        <v>-36.956521739130</v>
+        <v>-36.177474402730</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,17 +1100,17 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="14">
         <v>-100</v>
@@ -1119,19 +1119,19 @@
         <v>5</v>
       </c>
       <c r="J20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K20" s="14">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L20" s="14">
-        <v>-72.222222222222</v>
+        <v>-73.684210526315</v>
       </c>
       <c r="M20" s="14">
-        <v>-68.75</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.326203208556</v>
+        <v>-97.435897435897</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,57 +1139,57 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-27.272727272727</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G21" s="17">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.25</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J21" s="17">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.098265895953</v>
+        <v>-19.505494505494</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.098591549295</v>
+        <v>-21.866666666666</v>
       </c>
       <c r="M21" s="18">
-        <v>-15.479876160990</v>
+        <v>-13.056379821958</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.358306188925</v>
+        <v>-69.979508196721</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
         <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
-        <v>3</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>-10</v>
       </c>
       <c r="L22" s="14">
-        <v>-25</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M22" s="14">
         <v>200</v>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I23" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" s="15">
         <v>17</v>
       </c>
       <c r="K23" s="14">
-        <v>-11.764705882352</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L23" s="14">
-        <v>15.384615384615</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M23" s="14">
-        <v>-16.666666666666</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>19</v>
       </c>
       <c r="D24" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E24" s="14">
-        <v>35.714285714285</v>
+        <v>58.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G24" s="15">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="H24" s="14">
-        <v>13.698630136986</v>
+        <v>26.5625</v>
       </c>
       <c r="I24" s="15">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="J24" s="15">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="K24" s="14">
-        <v>8.540925266903</v>
+        <v>10.238907849829</v>
       </c>
       <c r="L24" s="14">
-        <v>51.741293532338</v>
+        <v>46.818181818181</v>
       </c>
       <c r="M24" s="14">
-        <v>14.232209737827</v>
+        <v>14.134275618374</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
+        <v>12</v>
+      </c>
+      <c r="D25" s="15">
         <v>9</v>
       </c>
-      <c r="D25" s="15">
-        <v>10</v>
-      </c>
       <c r="E25" s="14">
-        <v>-10</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F25" s="15">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G25" s="15">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H25" s="14">
-        <v>9.756097560975</v>
+        <v>34.285714285714</v>
       </c>
       <c r="I25" s="15">
+        <v>179</v>
+      </c>
+      <c r="J25" s="15">
         <v>166</v>
       </c>
-      <c r="J25" s="15">
-        <v>157</v>
-      </c>
       <c r="K25" s="14">
-        <v>5.732484076433</v>
+        <v>7.831325301204</v>
       </c>
       <c r="L25" s="14">
-        <v>86.516853932584</v>
+        <v>92.473118279569</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>-71.428571428571</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G26" s="15">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H26" s="14">
-        <v>-23.076923076923</v>
+        <v>-25</v>
       </c>
       <c r="I26" s="15">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J26" s="15">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K26" s="14">
-        <v>28.409090909090</v>
+        <v>23.404255319148</v>
       </c>
       <c r="L26" s="14">
-        <v>6.603773584905</v>
+        <v>5.454545454545</v>
       </c>
       <c r="M26" s="14">
-        <v>-5.042016806722</v>
+        <v>-7.2</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>8</v>
       </c>
       <c r="J27" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L27" s="14">
-        <v>-11.111111111111</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>3</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,10 +1438,10 @@
         <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I28" s="15">
         <v>20</v>
@@ -1453,7 +1453,7 @@
         <v>42.857142857142</v>
       </c>
       <c r="L28" s="14">
-        <v>5.263157894736</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
